--- a/cet4/result/81_教育女神_教师之光的传奇/81_教育女神_教师之光的传奇_学习版.xlsx
+++ b/cet4/result/81_教育女神_教师之光的传奇/81_教育女神_教师之光的传奇_学习版.xlsx
@@ -397,1179 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>ago</v>
       </c>
       <c r="B2" t="str">
-        <v>ago</v>
+        <v>/əˈɡoʊ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D2" t="str">
         <v>以前</v>
       </c>
-      <c r="D2" t="str">
-        <v>ago(以前)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>storey</v>
       </c>
       <c r="B3" t="str">
-        <v>storey</v>
+        <v>/ˈstɔːri/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>楼层</v>
       </c>
-      <c r="D3" t="str">
-        <v>storey(楼层)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>beach</v>
       </c>
       <c r="B4" t="str">
-        <v>beach</v>
+        <v>/biːtʃ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>海滩</v>
       </c>
-      <c r="D4" t="str">
-        <v>beach(海滩)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>mission</v>
       </c>
       <c r="B5" t="str">
-        <v>mission</v>
+        <v>/ˈmɪʃn/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D5" t="str">
         <v>使命</v>
       </c>
-      <c r="D5" t="str">
-        <v>mission(使命)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>boundary</v>
       </c>
       <c r="B6" t="str">
-        <v>boundary</v>
+        <v>/ˈbaʊndri/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>边界</v>
       </c>
-      <c r="D6" t="str">
-        <v>boundary(边界)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>surroundings</v>
       </c>
       <c r="B7" t="str">
-        <v>surroundings</v>
+        <v>/səˈraʊndɪŋz/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>环境</v>
       </c>
-      <c r="D7" t="str">
-        <v>surroundings(环境)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>dirt</v>
       </c>
       <c r="B8" t="str">
-        <v>dirt</v>
+        <v>/dɜːrt/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>污垢</v>
       </c>
-      <c r="D8" t="str">
-        <v>dirt(污垢)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>screw</v>
       </c>
       <c r="B9" t="str">
-        <v>screw</v>
+        <v>/skruː/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>螺丝钉</v>
       </c>
-      <c r="D9" t="str">
-        <v>screw(螺丝钉)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>eyesight</v>
       </c>
       <c r="B10" t="str">
-        <v>eyesight</v>
+        <v>/ˈaɪsaɪt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>视力</v>
       </c>
-      <c r="D10" t="str">
-        <v>eyesight(视力)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>welfare</v>
       </c>
       <c r="B11" t="str">
-        <v>welfare</v>
+        <v>/ˈwelfer/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>福利</v>
       </c>
-      <c r="D11" t="str">
-        <v>welfare(福利)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>anyone</v>
       </c>
       <c r="B12" t="str">
-        <v>anyone</v>
+        <v>/ˈeniwʌn/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D12" t="str">
         <v>任何人</v>
       </c>
-      <c r="D12" t="str">
-        <v>anyone(任何人)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>workshop</v>
       </c>
       <c r="B13" t="str">
-        <v>beach</v>
+        <v>/ˈwɜːrkʃɑːp/</v>
       </c>
       <c r="C13" t="str">
-        <v>海滩</v>
+        <v>n.</v>
       </c>
       <c r="D13" t="str">
-        <v>beach(海滩)📢</v>
+        <v>研讨会</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>shallow</v>
       </c>
       <c r="B14" t="str">
-        <v>workshop</v>
+        <v>/ˈʃæloʊ/</v>
       </c>
       <c r="C14" t="str">
-        <v>研讨会</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D14" t="str">
-        <v>workshop(研讨会)📢</v>
+        <v>浅的</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>eagle</v>
       </c>
       <c r="B15" t="str">
-        <v>shallow</v>
+        <v>/ˈiːɡl/</v>
       </c>
       <c r="C15" t="str">
-        <v>浅的</v>
+        <v>n.</v>
       </c>
       <c r="D15" t="str">
-        <v>shallow(浅的)📢</v>
+        <v>鹰</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>officer</v>
       </c>
       <c r="B16" t="str">
-        <v>beach</v>
+        <v>/ˈɑːfɪsər/</v>
       </c>
       <c r="C16" t="str">
-        <v>海滩</v>
+        <v>n./vt.</v>
       </c>
       <c r="D16" t="str">
-        <v>beach(海滩)📢</v>
+        <v>官员</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>commit</v>
       </c>
       <c r="B17" t="str">
-        <v>eagle</v>
+        <v>/kəˈmɪt/</v>
       </c>
       <c r="C17" t="str">
-        <v>鹰</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D17" t="str">
-        <v>eagle(鹰)📢</v>
+        <v>承诺</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>mark</v>
       </c>
       <c r="B18" t="str">
-        <v>officer</v>
+        <v>/mɑːrk/</v>
       </c>
       <c r="C18" t="str">
-        <v>官员</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D18" t="str">
-        <v>officer(官员)📢</v>
+        <v>痕迹</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>since</v>
       </c>
       <c r="B19" t="str">
-        <v>commit</v>
+        <v>/sɪns/</v>
       </c>
       <c r="C19" t="str">
-        <v>承诺</v>
+        <v>n./v./adv./prep./conj.</v>
       </c>
       <c r="D19" t="str">
-        <v>commit(承诺)📢</v>
+        <v>自从</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>accelerate</v>
       </c>
       <c r="B20" t="str">
-        <v>eagle</v>
+        <v>/əkˈseləreɪt/</v>
       </c>
       <c r="C20" t="str">
-        <v>鹰</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D20" t="str">
-        <v>eagle(鹰)📢</v>
+        <v>加速</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>quite</v>
       </c>
       <c r="B21" t="str">
-        <v>mark</v>
+        <v>/kwaɪt/</v>
       </c>
       <c r="C21" t="str">
-        <v>痕迹</v>
+        <v>v./adv.</v>
       </c>
       <c r="D21" t="str">
-        <v>mark(痕迹)📢</v>
+        <v>相当</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>maths</v>
       </c>
       <c r="B22" t="str">
-        <v>since</v>
+        <v>/mæθs/</v>
       </c>
       <c r="C22" t="str">
-        <v>自从</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>since(自从)📢</v>
+        <v>数学</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>diagram</v>
       </c>
       <c r="B23" t="str">
-        <v>accelerate</v>
+        <v>/ˈdaɪəɡræm/</v>
       </c>
       <c r="C23" t="str">
-        <v>加速</v>
+        <v>n./vt.</v>
       </c>
       <c r="D23" t="str">
-        <v>accelerate(加速)📢</v>
+        <v>图表</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>class</v>
       </c>
       <c r="B24" t="str">
-        <v>quite</v>
+        <v>/klæs/</v>
       </c>
       <c r="C24" t="str">
-        <v>相当</v>
+        <v>n./vt.</v>
       </c>
       <c r="D24" t="str">
-        <v>quite(相当)📢</v>
+        <v>班级</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>nearly</v>
       </c>
       <c r="B25" t="str">
-        <v>maths</v>
+        <v>/ˈnɪrli/</v>
       </c>
       <c r="C25" t="str">
-        <v>数学</v>
+        <v>v./adv.</v>
       </c>
       <c r="D25" t="str">
-        <v>maths(数学)📢</v>
+        <v>几乎</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>miss</v>
       </c>
       <c r="B26" t="str">
-        <v>diagram</v>
+        <v>/mɪs/</v>
       </c>
       <c r="C26" t="str">
-        <v>图表</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>diagram(图表)📢</v>
+        <v>错过</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>six</v>
       </c>
       <c r="B27" t="str">
-        <v>class</v>
+        <v>/sɪks/</v>
       </c>
       <c r="C27" t="str">
-        <v>班级</v>
+        <v>n./num.</v>
       </c>
       <c r="D27" t="str">
-        <v>class(班级)📢</v>
+        <v>六</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>thus</v>
       </c>
       <c r="B28" t="str">
-        <v>nearly</v>
+        <v>/ðʌs/</v>
       </c>
       <c r="C28" t="str">
-        <v>几乎</v>
+        <v>v./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>nearly(几乎)📢</v>
+        <v>因此</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>vanish</v>
       </c>
       <c r="B29" t="str">
-        <v>miss</v>
+        <v>/ˈvænɪʃ/</v>
       </c>
       <c r="C29" t="str">
-        <v>错过</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>miss(错过)📢</v>
+        <v>消失</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>another</v>
       </c>
       <c r="B30" t="str">
-        <v>six</v>
+        <v>/əˈnʌðər/</v>
       </c>
       <c r="C30" t="str">
-        <v>六</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D30" t="str">
-        <v>six(六)📢</v>
+        <v>另一个</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>royal</v>
       </c>
       <c r="B31" t="str">
-        <v>thus</v>
+        <v>/ˈrɔɪəl/</v>
       </c>
       <c r="C31" t="str">
-        <v>因此</v>
+        <v>n./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>thus(因此)📢</v>
+        <v>皇家的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>assemble</v>
       </c>
       <c r="B32" t="str">
-        <v>anyone</v>
+        <v>/əˈsembl/</v>
       </c>
       <c r="C32" t="str">
-        <v>任何人</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>anyone(任何人)📢</v>
+        <v>收集</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>catalog</v>
       </c>
       <c r="B33" t="str">
-        <v>nearly</v>
+        <v>/ˈkætəlɔːɡ/</v>
       </c>
       <c r="C33" t="str">
-        <v>几乎</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>nearly(几乎)📢</v>
+        <v>目录</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>handy</v>
       </c>
       <c r="B34" t="str">
-        <v>vanish</v>
+        <v>/ˈhændi/</v>
       </c>
       <c r="C34" t="str">
-        <v>消失</v>
+        <v>n./adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>vanish(消失)📢</v>
+        <v>便利的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>broadcast</v>
       </c>
       <c r="B35" t="str">
-        <v>another</v>
+        <v>/ˈbrɔːdkæst/</v>
       </c>
       <c r="C35" t="str">
-        <v>另一个</v>
+        <v>n./v.</v>
       </c>
       <c r="D35" t="str">
-        <v>another(另一个)📢</v>
+        <v>广播</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>coach</v>
       </c>
       <c r="B36" t="str">
-        <v>royal</v>
+        <v>/koʊtʃ/</v>
       </c>
       <c r="C36" t="str">
-        <v>皇家的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>royal(皇家的)📢</v>
+        <v>教练</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>supreme</v>
       </c>
       <c r="B37" t="str">
-        <v>six</v>
+        <v>/suːˈpriːm/</v>
       </c>
       <c r="C37" t="str">
-        <v>六</v>
+        <v>adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>six(六)📢</v>
+        <v>最高级别的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>treasure</v>
       </c>
       <c r="B38" t="str">
-        <v>assemble</v>
+        <v>/ˈtreʒər/</v>
       </c>
       <c r="C38" t="str">
-        <v>收集</v>
+        <v>n./vt.</v>
       </c>
       <c r="D38" t="str">
-        <v>assemble(收集)📢</v>
+        <v>财富</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>hers</v>
       </c>
       <c r="B39" t="str">
-        <v>catalog</v>
+        <v>/hɜːrz,ɜːrz/</v>
       </c>
       <c r="C39" t="str">
-        <v>目录</v>
+        <v>n./pron.</v>
       </c>
       <c r="D39" t="str">
-        <v>catalog(目录)📢</v>
+        <v>她的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>home</v>
       </c>
       <c r="B40" t="str">
-        <v>handy</v>
+        <v>/hoʊm/</v>
       </c>
       <c r="C40" t="str">
-        <v>便利的</v>
+        <v>n./vt./v./adj./adv.</v>
       </c>
       <c r="D40" t="str">
-        <v>handy(便利的)📢</v>
+        <v>中心</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>lever</v>
       </c>
       <c r="B41" t="str">
-        <v>broadcast</v>
+        <v>/ˈlevər/</v>
       </c>
       <c r="C41" t="str">
-        <v>广播</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>broadcast(广播)📢</v>
+        <v>杠杆</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>sober</v>
       </c>
       <c r="B42" t="str">
-        <v>coach</v>
+        <v>/ˈsoʊbər/</v>
       </c>
       <c r="C42" t="str">
-        <v>教练</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>coach(教练)📢</v>
+        <v>冷静的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>imitate</v>
       </c>
       <c r="B43" t="str">
-        <v>supreme</v>
+        <v>/ˈɪmɪteɪt/</v>
       </c>
       <c r="C43" t="str">
-        <v>最高级别的</v>
+        <v>vt.</v>
       </c>
       <c r="D43" t="str">
-        <v>supreme(最高级别的)📢</v>
+        <v>模仿</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>cock</v>
       </c>
       <c r="B44" t="str">
-        <v>officer</v>
+        <v>/kɑːk/</v>
       </c>
       <c r="C44" t="str">
-        <v>军官</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>officer(军官)📢</v>
+        <v>公鸡</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>speed</v>
       </c>
       <c r="B45" t="str">
-        <v>ago</v>
+        <v>/spiːd/</v>
       </c>
       <c r="C45" t="str">
-        <v>以前</v>
+        <v>n./v.</v>
       </c>
       <c r="D45" t="str">
-        <v>ago(以前)📢</v>
+        <v>快速</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>crane</v>
       </c>
       <c r="B46" t="str">
-        <v>officer</v>
+        <v>/kreɪn/</v>
       </c>
       <c r="C46" t="str">
-        <v>军官</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>officer(军官)📢</v>
+        <v>起重机</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>dispose</v>
       </c>
       <c r="B47" t="str">
-        <v>mission</v>
+        <v>/dɪˈspoʊz/</v>
       </c>
       <c r="C47" t="str">
-        <v>任务</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>mission(任务)📢</v>
+        <v>处理</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>sir</v>
       </c>
       <c r="B48" t="str">
-        <v>since</v>
+        <v>/sɜːr,sər/</v>
       </c>
       <c r="C48" t="str">
-        <v>自从</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>since(自从)📢</v>
+        <v>先生</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>regulate</v>
       </c>
       <c r="B49" t="str">
-        <v>treasure</v>
+        <v>/ˈreɡjuleɪt/</v>
       </c>
       <c r="C49" t="str">
-        <v>财富</v>
+        <v>vt.</v>
       </c>
       <c r="D49" t="str">
-        <v>treasure(财富)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>hers</v>
-      </c>
-      <c r="C50" t="str">
-        <v>她的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>hers(她的)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>home</v>
-      </c>
-      <c r="C51" t="str">
-        <v>中心</v>
-      </c>
-      <c r="D51" t="str">
-        <v>home(中心)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>mission</v>
-      </c>
-      <c r="C52" t="str">
-        <v>使命</v>
-      </c>
-      <c r="D52" t="str">
-        <v>mission(使命)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>lever</v>
-      </c>
-      <c r="C53" t="str">
-        <v>杠杆</v>
-      </c>
-      <c r="D53" t="str">
-        <v>lever(杠杆)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>workshop</v>
-      </c>
-      <c r="C54" t="str">
-        <v>工作室</v>
-      </c>
-      <c r="D54" t="str">
-        <v>workshop(工作室)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>sober</v>
-      </c>
-      <c r="C55" t="str">
-        <v>冷静的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>sober(冷静的)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>imitate</v>
-      </c>
-      <c r="C56" t="str">
-        <v>模仿</v>
-      </c>
-      <c r="D56" t="str">
-        <v>imitate(模仿)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>supreme</v>
-      </c>
-      <c r="C57" t="str">
-        <v>最高</v>
-      </c>
-      <c r="D57" t="str">
-        <v>supreme(最高)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>boundary</v>
-      </c>
-      <c r="C58" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D58" t="str">
-        <v>boundary(边界)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>welfare</v>
-      </c>
-      <c r="C59" t="str">
-        <v>幸福</v>
-      </c>
-      <c r="D59" t="str">
-        <v>welfare(幸福)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>hers</v>
-      </c>
-      <c r="C60" t="str">
-        <v>她</v>
-      </c>
-      <c r="D60" t="str">
-        <v>hers(她)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>cock</v>
-      </c>
-      <c r="C61" t="str">
-        <v>公鸡</v>
-      </c>
-      <c r="D61" t="str">
-        <v>cock(公鸡)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>speed</v>
-      </c>
-      <c r="C62" t="str">
-        <v>快速</v>
-      </c>
-      <c r="D62" t="str">
-        <v>speed(快速)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>workshop</v>
-      </c>
-      <c r="C63" t="str">
-        <v>工作室</v>
-      </c>
-      <c r="D63" t="str">
-        <v>workshop(工作室)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>catalog</v>
-      </c>
-      <c r="C64" t="str">
-        <v>目录</v>
-      </c>
-      <c r="D64" t="str">
-        <v>catalog(目录)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>ago</v>
-      </c>
-      <c r="C65" t="str">
-        <v>以前</v>
-      </c>
-      <c r="D65" t="str">
-        <v>ago(以前)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>catalog</v>
-      </c>
-      <c r="C66" t="str">
-        <v>目录</v>
-      </c>
-      <c r="D66" t="str">
-        <v>catalog(目录)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>sober</v>
-      </c>
-      <c r="C67" t="str">
-        <v>冷静的</v>
-      </c>
-      <c r="D67" t="str">
-        <v>sober(冷静的)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>crane</v>
-      </c>
-      <c r="C68" t="str">
-        <v>起重机</v>
-      </c>
-      <c r="D68" t="str">
-        <v>crane(起重机)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>crane</v>
-      </c>
-      <c r="C69" t="str">
-        <v>起重机</v>
-      </c>
-      <c r="D69" t="str">
-        <v>crane(起重机)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>crane</v>
-      </c>
-      <c r="C70" t="str">
-        <v>起重机</v>
-      </c>
-      <c r="D70" t="str">
-        <v>crane(起重机)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>commit</v>
-      </c>
-      <c r="C71" t="str">
-        <v>致力于</v>
-      </c>
-      <c r="D71" t="str">
-        <v>commit(致力于)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>nearly</v>
-      </c>
-      <c r="C72" t="str">
-        <v>几乎</v>
-      </c>
-      <c r="D72" t="str">
-        <v>nearly(几乎)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>dispose</v>
-      </c>
-      <c r="C73" t="str">
-        <v>处理</v>
-      </c>
-      <c r="D73" t="str">
-        <v>dispose(处理)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>treasure</v>
-      </c>
-      <c r="C74" t="str">
-        <v>财富</v>
-      </c>
-      <c r="D74" t="str">
-        <v>treasure(财富)📢</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>broadcast</v>
-      </c>
-      <c r="C75" t="str">
-        <v>广播</v>
-      </c>
-      <c r="D75" t="str">
-        <v>broadcast(广播)📢</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
-        <v>ago</v>
-      </c>
-      <c r="C76" t="str">
-        <v>以前</v>
-      </c>
-      <c r="D76" t="str">
-        <v>ago(以前)📢</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="str">
-        <v>royal</v>
-      </c>
-      <c r="C77" t="str">
-        <v>皇家</v>
-      </c>
-      <c r="D77" t="str">
-        <v>royal(皇家)📢</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="str">
-        <v>mission</v>
-      </c>
-      <c r="C78" t="str">
-        <v>使命</v>
-      </c>
-      <c r="D78" t="str">
-        <v>mission(使命)📢</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="str">
-        <v>sir</v>
-      </c>
-      <c r="C79" t="str">
-        <v>先生</v>
-      </c>
-      <c r="D79" t="str">
-        <v>sir(先生)📢</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="str">
-        <v>six</v>
-      </c>
-      <c r="C80" t="str">
-        <v>六</v>
-      </c>
-      <c r="D80" t="str">
-        <v>six(六)📢</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="str">
-        <v>diagram</v>
-      </c>
-      <c r="C81" t="str">
-        <v>图解</v>
-      </c>
-      <c r="D81" t="str">
-        <v>diagram(图解)📢</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="str">
-        <v>regulate</v>
-      </c>
-      <c r="C82" t="str">
         <v>规范</v>
-      </c>
-      <c r="D82" t="str">
-        <v>regulate(规范)📢</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="str">
-        <v>anyone</v>
-      </c>
-      <c r="C83" t="str">
-        <v>任何人</v>
-      </c>
-      <c r="D83" t="str">
-        <v>anyone(任何人)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>